--- a/帝国时代2决定版 文明联盟 步兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 步兵流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·步兵本体强化'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·步兵本体强化'!$A$1:$E$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·步兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与步兵流无关·可跳过'!$A$1:$D$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与步兵流无关·可跳过'!$1:$1</definedName>
@@ -1950,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1988,9 +1988,9 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2010,14 +2010,14 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2042,9 +2042,9 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击无视护甲，克制重甲目标</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>直接强化步兵</t>
+          <t>额外产出资源，经济滚雪球更快</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>直接强化步兵</t>
+          <t>额外产出资源，经济滚雪球更快</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2280,14 +2280,14 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>直接强化步兵</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2307,14 +2307,14 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>直接强化步兵</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2334,14 +2334,14 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>直接强化步兵</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2366,9 +2366,9 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2447,9 +2447,9 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2496,14 +2496,14 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2528,9 +2528,9 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2550,14 +2550,14 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2582,9 +2582,9 @@
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2604,876 +2604,903 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>吴</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>长矛兵系和掷矛手视野 +2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>步兵护甲升级免费</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>反弹近战伤害，换血更划算</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>步兵对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>步兵护甲升级效果加倍</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>古典解锁精锐希腊步兵</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>最小攻击范围缩小，贴身也能打</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>最小攻击范围缩小，贴身也能打</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>骑士系对步兵的攻击 +1</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对掷矛手攻+2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>希腊步兵移速+15%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>哈马思克（步兵失血时造成更多伤害）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>血量越低输出越高，残局更强</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>长矛兵系造成的额外伤害+25%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>在帝王时代可升级为帝王掷矛手</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>长矛兵系和掷矛手视野 +2</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>步兵护甲升级免费</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>步兵对远程士兵的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>步兵护甲升级效果加倍</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>古典解锁精锐希腊步兵</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>步兵护甲升级适用于骑兵</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>城堡起步兵铁匠铺升级影响村民</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>骑士系对步兵的攻击 +1</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>骑兵对掷矛手攻+2</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>希腊步兵移速+15%</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>哈马思克（步兵失血时造成更多伤害）</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>长矛兵系造成的额外伤害+25%</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>直接强化步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E56"/>
+  <autoFilter ref="A1:E57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3485,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3523,9 +3550,9 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3577,9 +3604,9 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3604,9 +3631,9 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3626,14 +3653,14 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>直接强化步兵</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3658,9 +3685,9 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3685,9 +3712,9 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3711,35 +3738,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/帝国时代2决定版 文明联盟 步兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 步兵流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·步兵本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与步兵流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·步兵本体强化'!$A$1:$E$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·步兵本体强化'!$A$1:$E$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·步兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与步兵流无关·可跳过'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与步兵流无关·可跳过'!$A$1:$D$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与步兵流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -587,12 +587,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>步兵黑暗/封建/城堡/帝王费用-15/20/25/30%；步兵封建/城堡/帝王对建筑攻+1/+2/+3</t>
+          <t>步兵封建/城堡/帝王对建筑攻+1/+2/+3；无政府（兵营训练侍从战士）；井喷（兵营生产速度+100%）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2 / 弱 3）；步兵科技树 11/15；缺 软甲、纵火、补给、板甲；最直接一条：步兵黑暗/封建/城堡/帝王费用-15/20/25/30%</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 3）；步兵科技树 11/15；缺 软甲、纵火、补给、板甲；最直接一条：步兵黑暗/封建/城堡/帝王费用-15/20/25/30%</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）</t>
+          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）；兵营科技-50%</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：皇家卫队（步兵可造成践踏伤害）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：皇家卫队（步兵可造成践踏伤害）</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 3 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：可提前一时代获长矛/民兵升级（武士除外）</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：可提前一时代获长矛/民兵升级（武士除外）</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>第 3 位</t>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+          <t>市政/古典掷矛手每分钟回5/10生命；奥多曼蒂突袭者（步兵/骑兵杀敌获金）；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 6 条（强 5 / 弱 1）；步兵科技树 6/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：精锐掷矛手升级免费</t>
+          <t>阶段1·本体强化；原生条目 11 条（强 5 / 弱 1）；步兵科技树 6/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：精锐掷矛手升级免费</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：民兵系升级免费</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：民兵系升级免费</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：皇家卫队（步兵可造成践踏伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：皇家卫队（步兵可造成践踏伤害）</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：可提前一时代获长矛/民兵升级（武士除外）</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：可提前一时代获长矛/民兵升级（武士除外）</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>民兵系升级免费；协议（民兵系近战护甲+5）</t>
+          <t>协议（民兵系近战护甲+5）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：民兵系升级免费</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：民兵系升级免费</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵封建/城堡/帝王攻+1/+2/+3</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵封建/城堡/帝王攻+1/+2/+3</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 12/15；缺 长戟兵、软甲、补给；最直接一条：封建起步兵生命+20%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 长戟兵、软甲、补给；最直接一条：封建起步兵生命+20%</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>每控制一个TC/城堡步兵花费-5%（最多-20%）；盾墙（步兵成群获额外护甲）</t>
+          <t>盾墙（步兵成群获额外护甲）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：步兵封建/城堡/帝王每分钟回10/15/30生命</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：步兵封建/城堡/帝王每分钟回10/15/30生命</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级免费；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
         </is>
       </c>
     </row>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
         </is>
       </c>
     </row>
@@ -1273,11 +1273,11 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>20</v>
       </c>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
+          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）；兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>21</v>
       </c>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>城堡起步兵铁匠铺升级影响村民；安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：骑士系对步兵的攻击 +1</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>长枪兵升级免费</t>
+          <t>骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、板甲；最直接一条：骑兵对掷矛手攻+2</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：骑士系对步兵的攻击 +1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>哈马思克（步兵失血时造成更多伤害）；兵营/攻城武器厂黄金升级-66%</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、板甲；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>哈马思克（步兵失血时造成更多伤害）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,27 +1593,27 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系造成的额外伤害+25%</t>
+          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="51" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,27 +1623,27 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="51" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
+          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 补给、铸铁、高炉；最直接一条：盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1713,27 +1713,27 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="51" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）；靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+          <t>在帝王时代兵营提供意大利佣兵</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 补给、铸铁、高炉；最直接一条：盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -1833,27 +1833,27 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%</t>
+          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代兵营提供意大利佣兵</t>
+          <t>远程/步兵木材费用-50%</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
+          <t>长枪兵升级免费</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -1923,22 +1923,52 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；步兵科技树 13/15；缺 纵火、补给</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1950,7 +1980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2022,22 +2052,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%</t>
+          <t>无政府（兵营训练侍从战士）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>直接强化步兵</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2079,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>乌兹钢（步兵和骑兵攻击无视护甲）</t>
+          <t>井喷（兵营生产速度+100%）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2064,7 +2094,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>攻击无视护甲，克制重甲目标</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -2076,22 +2106,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>市政/古典掷矛手每分钟回5/10生命</t>
+          <t>兵营生产速度 +20%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -2103,49 +2133,49 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+          <t>掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>乌兹钢（步兵和骑兵攻击无视护甲）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>额外产出资源，经济滚雪球更快</t>
+          <t>攻击无视护甲，克制重甲目标</t>
         </is>
       </c>
     </row>
@@ -2157,157 +2187,157 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>兵营科技-50%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>市政/古典掷矛手每分钟回5/10生命</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>封建起步兵攻速+33%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>荣冠战争（步兵攻击+4）</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>皇家卫队（步兵可造成践踏伤害）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2349,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>可提前一时代获长矛/民兵升级（武士除外）</t>
+          <t>封建起步兵攻速+33%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2334,7 +2364,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2346,22 +2376,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>费雷特斯（除长矛兵系外步兵生命+30；牧师战士治疗速度+100%）</t>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2373,22 +2403,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>步兵视野 +2</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -2400,22 +2430,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>荣冠战争（步兵攻击+4）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2427,157 +2457,157 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>皇家卫队（步兵可造成践踏伤害）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>亚美尼亚</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>可提前一时代获长矛/民兵升级（武士除外）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>亚美尼亚</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>费雷特斯（除长矛兵系外步兵生命+30；牧师战士治疗速度+100%）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>亚美尼亚</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>步兵视野 +2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>开垛口（城堡射程+3；驻扎的步兵射箭）</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>协议（民兵系近战护甲+5）</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>步兵封建/城堡/帝王攻+1/+2/+3</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>封建起步兵生命+20%</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>盾墙（步兵成群获额外护甲）</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2589,22 +2619,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>步兵封建/城堡/帝王每分钟回10/15/30生命</t>
+          <t>协议（民兵系近战护甲+5）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2646,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>步兵封建/城堡/帝王攻+1/+2/+3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2643,12 +2673,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
+          <t>封建起步兵生命+20%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2670,12 +2700,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2685,7 +2715,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>穿透伤害，对高护甲目标有效</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2697,26 +2727,26 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系和掷矛手视野 +2</t>
+          <t>盾墙（步兵成群获额外护甲）</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2724,12 +2754,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级免费</t>
+          <t>步兵封建/城堡/帝王每分钟回10/15/30生命</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2739,7 +2769,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -2751,22 +2781,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2808,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2793,7 +2823,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2835,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2820,7 +2850,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
@@ -2832,26 +2862,26 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>长矛兵系和掷矛手视野 +2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>反弹近战伤害，换血更划算</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2859,22 +2889,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>步兵对远程士兵的攻击力 +2</t>
+          <t>聚落可训长矛/掷矛</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2886,22 +2916,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级效果加倍</t>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -2913,184 +2943,184 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>反弹近战伤害，换血更划算</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>步兵对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>罗马</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>步兵护甲升级效果加倍</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>附加范围/冲击伤害，团战更占优</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>古典解锁精锐希腊步兵</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>步兵护甲升级适用于骑兵</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>最小攻击范围缩小，贴身也能打</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>城堡起步兵铁匠铺升级影响村民</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
         </is>
       </c>
     </row>
@@ -3102,44 +3132,44 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>古典解锁精锐希腊步兵</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>最小攻击范围缩小，贴身也能打</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>骑士系对步兵的攻击 +1</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3156,22 +3186,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -3183,22 +3213,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>希腊步兵移速+15%</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -3210,22 +3240,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>兵营科技研究速度 +50%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3267,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>哈马思克（步兵失血时造成更多伤害）</t>
+          <t>步兵护甲升级适用于骑兵</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>血量越低输出越高，残局更强</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3294,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3279,7 +3309,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>最小攻击范围缩小，贴身也能打</t>
         </is>
       </c>
     </row>
@@ -3291,216 +3321,675 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>兵营/靶场/马厩可用招募训令</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>最小攻击范围缩小，贴身也能打</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>骑士系对步兵的攻击 +1</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对掷矛手攻+2</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>希腊步兵移速+15%</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>哈马思克（步兵失血时造成更多伤害）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>血量越低输出越高，残局更强</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>波希米亚</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>在帝王时代可升级为帝王掷矛手</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>步弓/掷矛生命+20%</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>在帝王时代兵营提供意大利佣兵</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>长矛/掷矛移速+10%</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>塔盾（长矛/掷矛远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>减少受到的伤害，正面更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E57"/>
+  <autoFilter ref="A1:E74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3512,7 +4001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3657,20 +4146,20 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>步兵护甲升级免费</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3680,7 +4169,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
@@ -3692,54 +4181,135 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>远程/步兵木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>长枪兵升级免费</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3751,7 +4321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4027,12 +4597,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4042,19 +4612,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4064,19 +4634,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4086,19 +4656,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4108,19 +4678,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4130,19 +4700,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4152,19 +4722,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -4174,19 +4744,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4196,19 +4766,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4218,34 +4788,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强步兵</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
           <t>弓兵和象兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D22"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4725,7 +5273,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -4746,12 +5294,12 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>步兵黑暗/封建/城堡/帝王费用-15/20/25/30%；步兵封建/城堡/帝王对建筑攻+1/+2/+3</t>
+          <t>步兵封建/城堡/帝王对建筑攻+1/+2/+3；无政府（兵营训练侍从战士）；井喷（兵营生产速度+100%）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2 / 弱 3）；步兵科技树 11/15；缺 软甲、纵火、补给、板甲；最直接一条：步兵黑暗/封建/城堡/帝王费用-15/20/25/30%</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 3）；步兵科技树 11/15；缺 软甲、纵火、补给、板甲；最直接一条：步兵黑暗/封建/城堡/帝王费用-15/20/25/30%</t>
         </is>
       </c>
     </row>
@@ -4776,16 +5324,16 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）</t>
+          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）；兵营科技-50%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -4806,12 +5354,12 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+          <t>市政/古典掷矛手每分钟回5/10生命；奥多曼蒂突袭者（步兵/骑兵杀敌获金）；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 6 条（强 5 / 弱 1）；步兵科技树 6/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：精锐掷矛手升级免费</t>
+          <t>阶段1·本体强化；原生条目 11 条（强 5 / 弱 1）；步兵科技树 6/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：精锐掷矛手升级免费</t>
         </is>
       </c>
     </row>
@@ -4841,7 +5389,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
         </is>
       </c>
     </row>
@@ -4871,7 +5419,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -4901,7 +5449,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：皇家卫队（步兵可造成践踏伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：皇家卫队（步兵可造成践踏伤害）</t>
         </is>
       </c>
     </row>
@@ -4931,7 +5479,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：可提前一时代获长矛/民兵升级（武士除外）</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：可提前一时代获长矛/民兵升级（武士除外）</t>
         </is>
       </c>
     </row>
@@ -4961,7 +5509,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
     </row>
@@ -4986,12 +5534,12 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>民兵系升级免费；协议（民兵系近战护甲+5）</t>
+          <t>协议（民兵系近战护甲+5）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：民兵系升级免费</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：民兵系升级免费</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5569,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵封建/城堡/帝王攻+1/+2/+3</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：步兵封建/城堡/帝王攻+1/+2/+3</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5599,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 12/15；缺 长戟兵、软甲、补给；最直接一条：封建起步兵生命+20%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 长戟兵、软甲、补给；最直接一条：封建起步兵生命+20%</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5624,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>每控制一个TC/城堡步兵花费-5%（最多-20%）；盾墙（步兵成群获额外护甲）</t>
+          <t>盾墙（步兵成群获额外护甲）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5659,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：步兵封建/城堡/帝王每分钟回10/15/30生命</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：步兵封建/城堡/帝王每分钟回10/15/30生命</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5689,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5714,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级免费；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
         </is>
       </c>
     </row>
@@ -5201,11 +5749,11 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -5226,12 +5774,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5809,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
         </is>
       </c>
     </row>
@@ -5291,11 +5839,11 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -5316,16 +5864,16 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
+          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）；兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -5346,12 +5894,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>城堡起步兵铁匠铺升级影响村民；安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5909,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -5376,12 +5924,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：骑士系对步兵的攻击 +1</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5939,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -5406,12 +5954,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>长枪兵升级免费</t>
+          <t>骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、板甲；最直接一条：骑兵对掷矛手攻+2</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5969,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -5436,12 +5984,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：骑士系对步兵的攻击 +1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5999,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5466,12 +6014,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>哈马思克（步兵失血时造成更多伤害）；兵营/攻城武器厂黄金升级-66%</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、板甲；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
         </is>
       </c>
     </row>
@@ -5481,7 +6029,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -5496,12 +6044,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -5511,7 +6059,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5526,12 +6074,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>哈马思克（步兵失血时造成更多伤害）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +6089,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5556,12 +6104,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
     </row>
@@ -5571,7 +6119,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -5586,12 +6134,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -5601,7 +6149,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -5616,22 +6164,22 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系造成的额外伤害+25%</t>
+          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -5646,22 +6194,22 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="51" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -5676,12 +6224,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -5691,7 +6239,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -5706,22 +6254,22 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
+          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 补给、铸铁、高炉；最直接一条：盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="51" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -5736,22 +6284,22 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="51" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -5766,12 +6314,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）；靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -5781,7 +6329,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -5796,12 +6344,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+          <t>在帝王时代兵营提供意大利佣兵</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 12/15；缺 补给、铸铁、高炉；最直接一条：盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -5811,7 +6359,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -5826,12 +6374,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
         </is>
       </c>
     </row>
@@ -5841,7 +6389,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -5856,22 +6404,22 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%</t>
+          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -5886,12 +6434,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代兵营提供意大利佣兵</t>
+          <t>远程/步兵木材费用-50%</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
         </is>
       </c>
     </row>
@@ -5901,7 +6449,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -5916,12 +6464,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
+          <t>长枪兵升级免费</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -5931,7 +6479,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -5946,12 +6494,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；步兵科技树 13/15；缺 纵火、补给</t>
         </is>
       </c>
     </row>
@@ -5961,7 +6509,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -5971,17 +6519,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强步兵</t>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6539,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -6011,7 +6559,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6569,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -6041,7 +6589,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6599,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -6071,7 +6619,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6629,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -6101,7 +6649,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6659,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -6131,7 +6679,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6689,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -6161,7 +6709,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6719,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -6191,7 +6739,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6749,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -6221,7 +6769,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6779,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -6251,7 +6799,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6809,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -6281,7 +6829,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6839,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -6311,7 +6859,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -6598,7 +7146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6717,101 +7265,141 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于步兵本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与步兵流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="12" t="inlineStr"/>
+          <t>直接加强步兵本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（步兵系（民兵/长矛/掷矛等））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
-      <c r="B15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与步兵流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="12" t="inlineStr"/>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 步兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 步兵流最优研究顺序 By RemonBo.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·步兵本体强化'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·步兵本体强化'!$A$1:$E$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·步兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与步兵流无关·可跳过'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与步兵流无关·可跳过'!$A$1:$D$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与步兵流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -606,7 +606,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）；兵营科技-50%</t>
+          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>封建起步兵攻速+33%；骑射手对远程攻+2（掷矛手除外）</t>
+          <t>封建起步兵攻速+33%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,27 +1143,27 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%；堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,27 +1173,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%；堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2；掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>步兵护甲升级效果加倍；野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1213,17 +1213,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,27 +1233,27 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级效果加倍；野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>古典解锁精锐希腊步兵；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>古典时代起</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="66" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,27 +1263,27 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>古典解锁精锐希腊步兵；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
+          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）；兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>古典时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）；兵营/靶场/马厩可用招募训令</t>
+          <t>城堡起步兵铁匠铺升级影响村民；安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
+          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：骑士系对步兵的攻击 +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、板甲；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>哈马思克（步兵失血时造成更多伤害）；兵营/攻城武器厂黄金升级-66%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系造成的额外伤害+25%</t>
+          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,27 +1593,27 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
+          <t>哈马思克（步兵失血时造成更多伤害）</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,27 +1623,27 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
     </row>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="51" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1713,27 +1713,27 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1743,17 +1743,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>卡西克（蔷琵战士/投石手攻速+25%）；靶场/兵营升级食物-50%</t>
+          <t>在帝王时代兵营提供意大利佣兵</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代兵营提供意大利佣兵</t>
+          <t>步兵护甲升级免费；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
+          <t>阶段2·减费用；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
+          <t>远程/步兵木材费用-50%</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>长枪兵升级免费</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>长枪兵升级免费</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1903,72 +1903,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>所有单位黄金费用-20%</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
           <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；步兵科技树 13/15；缺 纵火、补给</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F40"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1980,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2187,12 +2127,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>兵营科技-50%</t>
+          <t>市政/古典掷矛手每分钟回5/10生命</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2202,7 +2142,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -2219,125 +2159,125 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>市政/古典掷矛手每分钟回5/10生命</t>
+          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>轻装盾兵（掷矛手造成穿透伤害）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>封建起步兵攻速+33%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>持续回血，长期更省维修成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>轻装盾兵（掷矛手造成穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2349,22 +2289,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>封建起步兵攻速+33%</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -2376,17 +2316,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>荣冠战争（步兵攻击+4）</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2403,12 +2343,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>皇家卫队（步兵可造成践踏伤害）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2418,7 +2358,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -2430,22 +2370,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>荣冠战争（步兵攻击+4）</t>
+          <t>可提前一时代获长矛/民兵升级（武士除外）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2397,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>皇家卫队（步兵可造成践踏伤害）</t>
+          <t>费雷特斯（除长矛兵系外步兵生命+30；牧师战士治疗速度+100%）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2472,7 +2412,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2489,17 +2429,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>可提前一时代获长矛/民兵升级（武士除外）</t>
+          <t>步兵视野 +2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2511,22 +2451,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>费雷特斯（除长矛兵系外步兵生命+30；牧师战士治疗速度+100%）</t>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2538,76 +2478,76 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>步兵视野 +2</t>
+          <t>开垛口（城堡射程+3；驻扎的步兵射箭）</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>协议（民兵系近战护甲+5）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>步兵封建/城堡/帝王攻+1/+2/+3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>开垛口（城堡射程+3；驻扎的步兵射箭）</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2619,22 +2559,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>协议（民兵系近战护甲+5）</t>
+          <t>封建起步兵生命+20%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2646,17 +2586,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>步兵封建/城堡/帝王攻+1/+2/+3</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2673,22 +2613,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>封建起步兵生命+20%</t>
+          <t>盾墙（步兵成群获额外护甲）</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2700,22 +2640,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>步兵封建/城堡/帝王每分钟回10/15/30生命</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -2727,22 +2667,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>盾墙（步兵成群获额外护甲）</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2694,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>步兵封建/城堡/帝王每分钟回10/15/30生命</t>
+          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2769,7 +2709,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2781,22 +2721,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
@@ -2813,44 +2753,44 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
+          <t>长矛兵系和掷矛手视野 +2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>穿透伤害，对高护甲目标有效</t>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2862,26 +2802,26 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系和掷矛手视野 +2</t>
+          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2889,22 +2829,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>聚落可训长矛/掷矛</t>
+          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2856,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2931,7 +2871,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>反弹近战伤害，换血更划算</t>
         </is>
       </c>
     </row>
@@ -2943,22 +2883,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+          <t>步兵对远程士兵的攻击力 +2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2970,22 +2910,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2997,22 +2937,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>步兵护甲升级效果加倍</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>反弹近战伤害，换血更划算</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -3024,22 +2964,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>步兵对远程士兵的攻击力 +2</t>
+          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -3051,12 +2991,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>古典解锁精锐希腊步兵</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3066,11 +3006,11 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -3078,22 +3018,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级效果加倍</t>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3045,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3120,14 +3060,14 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3137,24 +3077,24 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>古典解锁精锐希腊步兵</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3164,17 +3104,17 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+          <t>兵营科技研究速度 +50%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3126,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
+          <t>步兵护甲升级适用于骑兵</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3213,12 +3153,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3228,7 +3168,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>最小攻击范围缩小，贴身也能打</t>
         </is>
       </c>
     </row>
@@ -3240,26 +3180,26 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>兵营科技研究速度 +50%</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>研究/生产速度提升，科技与产能来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -3267,12 +3207,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级适用于骑兵</t>
+          <t>城堡起步兵铁匠铺升级影响村民</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3282,7 +3222,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3234,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>马其顿方阵步兵（方阵步兵最小攻击范围减半）</t>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3321,26 +3261,26 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -3348,22 +3288,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>最小攻击范围缩小，贴身也能打</t>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -3375,22 +3315,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
+          <t>步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -3402,22 +3342,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>长矛/掷矛移速+10%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -3429,22 +3369,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>塔盾（长矛/掷矛远程护甲+2）</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -3456,22 +3396,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>希腊步兵移速+15%</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3423,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3498,7 +3438,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -3510,22 +3450,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>哈马思克（步兵失血时造成更多伤害）</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>血量越低输出越高，残局更强</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -3537,22 +3477,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3504,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3579,7 +3519,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3531,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>希腊步兵移速+15%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3606,7 +3546,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -3618,22 +3558,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系造成的额外伤害+25%</t>
+          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -3645,80 +3585,80 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>哈马思克（步兵失血时造成更多伤害）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>血量越低输出越高，残局更强</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>长矛兵系造成的额外伤害+25%</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>步弓/掷矛生命+20%</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
+    <row r="65" ht="36" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>D</t>
@@ -3726,12 +3666,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3741,7 +3681,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>减少受到的伤害，正面更耐打</t>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3693,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3768,7 +3708,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -3780,26 +3720,26 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>盘蛇阵（长矛兵系/白毦卫靠近时获额外生命）</t>
+          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>D</t>
@@ -3807,189 +3747,27 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>在帝王时代兵营提供意大利佣兵</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>靶场/兵营升级食物-50%</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>意大利</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>在帝王时代兵营提供意大利佣兵</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
           <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>长矛/掷矛移速+10%</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>塔盾（长矛/掷矛远程护甲+2）</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E74"/>
+  <autoFilter ref="A1:E68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4001,7 +3779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4065,7 +3843,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>S</t>
@@ -4073,147 +3851,147 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>兵营科技-50%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>精锐掷矛手升级免费</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>保加利亚</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>民兵系升级免费</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>每控制一个TC/城堡步兵花费-5%（最多-20%）</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>步兵护甲升级免费</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>城堡起步兵铁匠铺升级影响村民</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4235,12 +4013,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>长枪兵升级免费</t>
+          <t>步兵护甲升级免费</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4262,54 +4040,135 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>远程/步兵木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>长枪兵升级免费</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4321,7 +4180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4553,12 +4412,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4568,19 +4427,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4590,19 +4449,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>骑兵和火药文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4612,19 +4471,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4634,19 +4493,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4656,19 +4515,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4678,19 +4537,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4700,19 +4559,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4722,19 +4581,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -4744,19 +4603,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4766,34 +4625,78 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>骆驼和火药文明</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强步兵</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>步弓手和火药文明</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强步兵</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>弓兵和象兵文明</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>无一条直接加强步兵</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>弓兵和象兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4933,12 +4836,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>封建起步兵攻速+33%；骑射手对远程攻+2（掷矛手除外）</t>
+          <t>封建起步兵攻速+33%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；步兵科技树 14/15。缺：补给</t>
+          <t>原生条目 1 条（强 1）；步兵科技树 14/15。缺：补给</t>
         </is>
       </c>
     </row>
@@ -5198,22 +5101,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级免费；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%；堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；步兵科技树 12/15。缺：冠军剑士、软甲、补给</t>
+          <t>原生条目 2 条（强 2）；步兵科技树 13/15。缺：纵火、补给</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5227,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）；兵营科技-50%</t>
+          <t>掷矛手/骑象弓兵攻速+25%；乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -5384,12 +5287,12 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>封建起步兵攻速+33%；骑射手对远程攻+2（掷矛手除外）</t>
+          <t>封建起步兵攻速+33%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：封建起步兵攻速+33%</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5602,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5714,22 +5617,22 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%；堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5744,22 +5647,22 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>步兵黑暗/封建/城堡/帝王移速+5/10/15/20%；堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 13/15；缺 纵火、补给；最直接一条：步兵黑暗/封建/城堡/帝王移速+5/10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -5774,22 +5677,22 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）；步兵对远程士兵的攻击力 +2；掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>步兵护甲升级效果加倍；野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 12/15；缺 长戟兵、补给、高炉；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -5804,22 +5707,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级效果加倍；野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>古典解锁精锐希腊步兵；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 9/15；缺 冠军剑士、双手剑士、软甲、纵火；最直接一条：步兵护甲升级效果加倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="66" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -5834,22 +5737,22 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>古典解锁精锐希腊步兵；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）</t>
+          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）；兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 2）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：古典解锁精锐希腊步兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -5864,22 +5767,22 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级适用于骑兵；马其顿方阵步兵（方阵步兵最小攻击范围减半）；兵营/靶场/马厩可用招募训令</t>
+          <t>城堡起步兵铁匠铺升级影响村民；安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；步兵科技树 8/15；缺 冠军剑士、双手剑士、长戟兵、长矛兵；最直接一条：步兵护甲升级适用于骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -5894,12 +5797,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
+          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；步兵科技树 11/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：城堡起步兵铁匠铺升级影响村民</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5812,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -5924,22 +5827,22 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 冠军剑士、补给；最直接一条：骑士系对步兵的攻击 +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -5954,12 +5857,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、板甲；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5872,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -5984,12 +5887,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5902,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -6014,22 +5917,22 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>哈马思克（步兵失血时造成更多伤害）；兵营/攻城武器厂黄金升级-66%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -6044,22 +5947,22 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 14/15；缺 补给；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="51" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -6074,12 +5977,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -6089,7 +5992,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -6104,22 +6007,22 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系造成的额外伤害+25%</t>
+          <t>希腊步兵移速+15%；军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 双手剑士、软甲、补给；最直接一条：希腊步兵移速+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="51" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -6134,12 +6037,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 长戟兵、补给；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6052,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -6164,22 +6067,22 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
+          <t>哈马思克（步兵失血时造成更多伤害）</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；步兵科技树 14/15；缺 补给；最直接一条：哈马思克（步兵失血时造成更多伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -6194,22 +6097,22 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>长矛兵系造成的额外伤害+25%</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、双手剑士、补给；最直接一条：堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：长矛兵系造成的额外伤害+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -6224,12 +6127,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
     </row>
@@ -6263,13 +6166,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="51" customHeight="1">
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -6284,22 +6187,22 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
+          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：波斯步兵方阵（长生军/长矛兵护甲+2/+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -6314,12 +6217,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>卡西克（蔷琵战士/投石手攻速+25%）；靶场/兵营升级食物-50%</t>
+          <t>在帝王时代兵营提供意大利佣兵</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；步兵科技树 10/15；缺 冠军剑士、双手剑士、软甲、补给；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6232,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -6344,12 +6247,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代兵营提供意大利佣兵</t>
+          <t>步兵护甲升级免费；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 12/15；缺 长戟兵、软甲、补给</t>
+          <t>阶段2·减费用；原生条目 4 条（强 2 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给；最直接一条：步兵护甲升级免费</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6262,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -6374,12 +6277,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>长矛/掷矛移速+10%；塔盾（长矛/掷矛远程护甲+2）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；步兵科技树 11/15；缺 软甲、补给、高炉、板甲</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 补给、高炉；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6292,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -6404,12 +6307,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>兵营单位封建/城堡/帝王远程护甲+1/+2/+3</t>
+          <t>远程/步兵木材费用-50%</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；步兵科技树 11/15；缺 长戟兵、软甲、补给、高炉</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6322,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -6434,12 +6337,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>长枪兵升级免费</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；步兵科技树 12/15；缺 软甲、补给、高炉；最直接一条：远程/步兵木材费用-50%</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6352,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -6464,12 +6367,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>长枪兵升级免费</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；步兵科技树 12/15；缺 冠军剑士、软甲、补给</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；步兵科技树 13/15；缺 纵火、补给</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6382,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -6489,17 +6392,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>无一条直接加强步兵</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；步兵科技树 13/15；缺 纵火、补给</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6412,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -6519,17 +6422,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>无一条直接加强步兵</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；步兵科技树 13/15；缺 软甲、补给；最直接一条：弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6442,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -6559,7 +6462,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6472,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -6589,7 +6492,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6502,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -6619,7 +6522,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6532,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -6649,7 +6552,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6562,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -6679,7 +6582,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6592,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -6709,7 +6612,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6622,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -6739,7 +6642,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6652,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -6769,7 +6672,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6682,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -6799,7 +6702,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6712,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -6829,7 +6732,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6742,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -6859,7 +6762,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6772,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -6889,7 +6792,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6802,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -6919,7 +6822,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于步兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
